--- a/stock_choose/output/短期选股_20260930.xlsx
+++ b/stock_choose/output/短期选股_20260930.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,6 +486,518 @@
         <is>
           <t>final_score</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>301716.SZ</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>C鸿富诚</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="n">
+        <v>3.406422833615383</v>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="n">
+        <v>5.05512287918544</v>
+      </c>
+      <c r="G2" t="n">
+        <v>-0.2651443259056016</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.6486482191622416</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.637708632436502</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>多方占优</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="n">
+        <v>2.687708632436502</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>688685.SH</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>迈信林</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1.117983448822805</v>
+      </c>
+      <c r="D3" t="n">
+        <v>3.131254046716214</v>
+      </c>
+      <c r="E3" t="n">
+        <v>4.647885767769844</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2.335833164893481</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-0.3057335797655475</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.646515368366023</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.411611887249254</v>
+      </c>
+      <c r="J3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>底部放量 MACD死叉 KDJ金叉 均线破位 多方占优</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>放量上影线 MACD金叉</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>2.651611887249254</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>300804.SZ</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>广康生化</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>3.107863775074621</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.7834883824565863</v>
+      </c>
+      <c r="E4" t="n">
+        <v>4.647885767769844</v>
+      </c>
+      <c r="F4" t="n">
+        <v>5.05512287918544</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-0.4502026130386014</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.646515368366023</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.720786866915435</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>MACD死叉 KDJ金叉 多方占优</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>均线多头 MACD金叉 BOLL站上中轨</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>2.650786866915436</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>600657.SH</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>信达地产</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>3.486892383378624</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.550801088382848</v>
+      </c>
+      <c r="E5" t="n">
+        <v>4.647885767769844</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1.702936238676699</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-0.1749071406939663</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.646515368366023</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.713935059305944</v>
+      </c>
+      <c r="J5" t="n">
+        <v>4</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>多方占优</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>均线多头 MACD金叉 BOLL站上中轨</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>2.533935059305944</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>301080.SZ</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>百普赛斯</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>3.898619385471023</v>
+      </c>
+      <c r="D6" t="n">
+        <v>3.406422833615383</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.7043466491214116</v>
+      </c>
+      <c r="F6" t="n">
+        <v>4.948597700582523</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.07376856718699339</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.646515368366023</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.693641628583468</v>
+      </c>
+      <c r="J6" t="n">
+        <v>5</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>KDJ金叉 多方占优</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>均线多头 放量上影线 BOLL站上中轨</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>2.523641628583468</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>600719.SH</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>大连热电</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>2.623997897212685</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.399846455187725</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3.28984580638098</v>
+      </c>
+      <c r="F7" t="n">
+        <v>4.944115327750182</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-0.3860446292302455</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.646515368366023</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.707368890690877</v>
+      </c>
+      <c r="J7" t="n">
+        <v>6</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>KDJ金叉 多方占优</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>均线多头 放量上影线 MACD金叉 BOLL站上中轨</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>2.497368890690877</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>300905.SZ</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>宝丽迪</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1.877351459310384</v>
+      </c>
+      <c r="D8" t="n">
+        <v>3.126258938467567</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2.50636121327202</v>
+      </c>
+      <c r="F8" t="n">
+        <v>3.628874197063792</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-0.3139393990446808</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.646515368366023</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.371134925774332</v>
+      </c>
+      <c r="J8" t="n">
+        <v>7</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>底部放量 KDJ金叉</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>均线多头 放量上影线 BOLL站上中轨</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>2.261134925774332</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>002487.SZ</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>大金重工</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>3.898619385471023</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.391109874807305</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.8610435677432038</v>
+      </c>
+      <c r="F9" t="n">
+        <v>4.402736454716544</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.4358617525730438</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.646515368366023</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.367567064342136</v>
+      </c>
+      <c r="J9" t="n">
+        <v>8</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>底部放量 KDJ金叉</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>均线多头 放量上影线 BOLL站上中轨</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>2.257567064342136</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>301047.SZ</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>义翘神州</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>3.898619385471023</v>
+      </c>
+      <c r="D10" t="n">
+        <v>3.406422833615383</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.469301271188724</v>
+      </c>
+      <c r="F10" t="n">
+        <v>3.421449747176661</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.109631188612063</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.646515368366023</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.437768299664217</v>
+      </c>
+      <c r="J10" t="n">
+        <v>9</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>多方占优</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>均线多头 放量上影线 BOLL站上中轨</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>2.247768299664217</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>300725.SZ</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>药石科技</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>3.127361782541296</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.372969403865406</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.9393920270540999</v>
+      </c>
+      <c r="F11" t="n">
+        <v>5.012586219834755</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-0.1398116134907177</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.990682869040231</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.30444469446849</v>
+      </c>
+      <c r="J11" t="n">
+        <v>10</v>
+      </c>
+      <c r="K11" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>多方占优</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>均线多头 BOLL站上中轨</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>2.16444469446849</v>
       </c>
     </row>
   </sheetData>
